--- a/research/traditional_assets/database/data/turkey/turkey_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_insurance_prop_cas.xlsx
@@ -588,124 +588,112 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.266</v>
+        <v>0.279</v>
       </c>
       <c r="E2">
-        <v>0.2585</v>
+        <v>0.388</v>
       </c>
       <c r="F2">
-        <v>0.08500000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G2">
-        <v>0.08598775424027025</v>
+        <v>-0.1290203918432627</v>
       </c>
       <c r="H2">
-        <v>0.08598775424027025</v>
+        <v>-0.1290203918432627</v>
       </c>
       <c r="I2">
-        <v>0.05015637886728639</v>
+        <v>-0.2409671815703175</v>
       </c>
       <c r="J2">
-        <v>0.03829674844665686</v>
+        <v>-0.2182798571441057</v>
       </c>
       <c r="K2">
-        <v>91.81</v>
+        <v>24.13</v>
       </c>
       <c r="L2">
-        <v>0.06461397705679499</v>
+        <v>0.02412035185925629</v>
       </c>
       <c r="M2">
-        <v>53.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.08061362610918935</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.5838143993029081</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>53.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.08061362610918935</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.5838143993029081</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>609.6</v>
+        <v>346.1</v>
       </c>
       <c r="V2">
-        <v>0.9168295984358551</v>
+        <v>0.4655010087424344</v>
       </c>
       <c r="W2">
-        <v>0.190040278286342</v>
+        <v>0.1259681093394077</v>
       </c>
       <c r="X2">
-        <v>0.09335742948749436</v>
+        <v>0.1589646499030975</v>
       </c>
       <c r="Y2">
-        <v>0.09668284879884763</v>
-      </c>
-      <c r="Z2">
-        <v>-11.72301762530756</v>
-      </c>
-      <c r="AA2">
-        <v>-0.6467286187822757</v>
+        <v>-0.03299654056368978</v>
       </c>
       <c r="AB2">
-        <v>0.09278025572916694</v>
-      </c>
-      <c r="AC2">
-        <v>-0.7403399950228153</v>
+        <v>0.1579874891624672</v>
       </c>
       <c r="AD2">
-        <v>11.48</v>
+        <v>26.075</v>
       </c>
       <c r="AE2">
-        <v>5.40400633736386</v>
+        <v>2.492842214728361</v>
       </c>
       <c r="AF2">
-        <v>16.88400633736386</v>
+        <v>28.56784221472836</v>
       </c>
       <c r="AG2">
-        <v>-592.7159936626362</v>
+        <v>-317.5321577852716</v>
       </c>
       <c r="AH2">
-        <v>0.02476445058907591</v>
+        <v>0.03700172530535605</v>
       </c>
       <c r="AI2">
-        <v>0.03690622208312357</v>
+        <v>0.09174949478253164</v>
       </c>
       <c r="AJ2">
-        <v>-8.211181724833621</v>
+        <v>-0.7454369234408195</v>
       </c>
       <c r="AK2">
-        <v>3.896473864393021</v>
+        <v>9.142310125054294</v>
       </c>
       <c r="AL2">
-        <v>7.48</v>
+        <v>5.72</v>
       </c>
       <c r="AM2">
-        <v>7.48</v>
+        <v>5.72</v>
       </c>
       <c r="AN2">
-        <v>0.1342250491067253</v>
+        <v>-0.1123026896655684</v>
       </c>
       <c r="AO2">
-        <v>9.617647058823529</v>
+        <v>-42.11013986013986</v>
       </c>
       <c r="AP2">
-        <v>-6.930081302762091</v>
+        <v>1.367582564701732</v>
       </c>
       <c r="AQ2">
-        <v>9.617647058823529</v>
+        <v>-42.11013986013986</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ray Sigorta Anonim Sirketi (IBSE:RAYSG)</t>
+          <t>Anadolu Anonim Türk Sigorta Sirketi (IBSE:ANSGR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,28 +713,31 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.272</v>
+        <v>0.266</v>
       </c>
       <c r="E3">
-        <v>0.126</v>
+        <v>0.409</v>
+      </c>
+      <c r="F3">
+        <v>0.05</v>
       </c>
       <c r="G3">
-        <v>0.08807947019867551</v>
+        <v>-0.1946138967415563</v>
       </c>
       <c r="H3">
-        <v>0.08807947019867551</v>
+        <v>-0.1946138967415563</v>
       </c>
       <c r="I3">
-        <v>0.04017660044150111</v>
+        <v>-0.2541192805281143</v>
       </c>
       <c r="J3">
-        <v>0.0276818157681133</v>
+        <v>-0.2169518345768567</v>
       </c>
       <c r="K3">
-        <v>4.01</v>
+        <v>43.4</v>
       </c>
       <c r="L3">
-        <v>0.04426048565121413</v>
+        <v>0.06457372414819224</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -770,67 +761,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>96.7</v>
+        <v>178.2</v>
       </c>
       <c r="V3">
-        <v>0.5674882629107981</v>
+        <v>0.4145150034891835</v>
       </c>
       <c r="W3">
-        <v>0.09218390804597701</v>
+        <v>0.1546685673556664</v>
       </c>
       <c r="X3">
-        <v>0.09255413140183148</v>
+        <v>0.1589646499030975</v>
       </c>
       <c r="Y3">
-        <v>-0.0003702233558544737</v>
-      </c>
-      <c r="Z3">
-        <v>-1.913006756756757</v>
-      </c>
-      <c r="AA3">
-        <v>-0.05295550060369649</v>
+        <v>-0.004296082547431107</v>
       </c>
       <c r="AB3">
-        <v>0.09246412135575853</v>
-      </c>
-      <c r="AC3">
-        <v>-0.145419621959455</v>
+        <v>0.1579874891624672</v>
       </c>
       <c r="AD3">
-        <v>0.47</v>
+        <v>4.47</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>2.492842214728361</v>
       </c>
       <c r="AF3">
-        <v>0.47</v>
+        <v>6.962842214728361</v>
       </c>
       <c r="AG3">
-        <v>-96.23</v>
+        <v>-171.2371577852716</v>
       </c>
       <c r="AH3">
-        <v>0.002750629133259203</v>
+        <v>0.01593827980294547</v>
       </c>
       <c r="AI3">
-        <v>0.01059274284426414</v>
+        <v>0.03720205427709857</v>
       </c>
       <c r="AJ3">
-        <v>-1.297424834838884</v>
+        <v>-0.6620091093065447</v>
       </c>
       <c r="AK3">
-        <v>1.838906936747563</v>
+        <v>-19.10522953353823</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="AN3">
-        <v>0.1017316017316017</v>
+        <v>-0.02707532027014749</v>
+      </c>
+      <c r="AO3">
+        <v>-29.82517482517483</v>
       </c>
       <c r="AP3">
-        <v>-20.82900432900433</v>
+        <v>1.037203778341389</v>
+      </c>
+      <c r="AQ3">
+        <v>-29.82517482517483</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anadolu Anonim Türk Sigorta Sirketi (IBSE:ANSGR)</t>
+          <t>Aksigorta A.S. (IBSE:AKGRT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,124 +838,100 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.193</v>
-      </c>
-      <c r="E4">
-        <v>0.391</v>
-      </c>
-      <c r="F4">
-        <v>0.07000000000000001</v>
+        <v>0.279</v>
       </c>
       <c r="G4">
-        <v>0.04220994475138122</v>
+        <v>0.009774143302180684</v>
       </c>
       <c r="H4">
-        <v>0.04220994475138122</v>
+        <v>0.009774143302180684</v>
       </c>
       <c r="I4">
-        <v>0.02776486047793064</v>
+        <v>-0.2655763239875389</v>
       </c>
       <c r="J4">
-        <v>0.02280057371526266</v>
+        <v>-0.2655763239875389</v>
       </c>
       <c r="K4">
-        <v>51.9</v>
+        <v>-24.8</v>
       </c>
       <c r="L4">
-        <v>0.05734806629834254</v>
+        <v>-0.09657320872274143</v>
       </c>
       <c r="M4">
-        <v>19.2</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.07717041800643086</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.3699421965317919</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>19.2</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.07717041800643086</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.3699421965317919</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>293.4</v>
+        <v>110.8</v>
       </c>
       <c r="V4">
-        <v>1.179260450160772</v>
+        <v>0.8683385579937304</v>
       </c>
       <c r="W4">
-        <v>0.190040278286342</v>
+        <v>-0.2136089577950043</v>
       </c>
       <c r="X4">
-        <v>0.09550078910431499</v>
+        <v>0.1726679379346905</v>
       </c>
       <c r="Y4">
-        <v>0.094539489182027</v>
-      </c>
-      <c r="Z4">
-        <v>-28.36457656104315</v>
-      </c>
-      <c r="AA4">
-        <v>-0.6467286187822757</v>
+        <v>-0.3862768957296948</v>
       </c>
       <c r="AB4">
-        <v>0.09361137624053963</v>
-      </c>
-      <c r="AC4">
-        <v>-0.7403399950228153</v>
+        <v>0.1628254198154563</v>
       </c>
       <c r="AD4">
-        <v>7.14</v>
+        <v>21.2</v>
       </c>
       <c r="AE4">
-        <v>5.40400633736386</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>12.54400633736386</v>
+        <v>21.2</v>
       </c>
       <c r="AG4">
-        <v>-280.8559936626361</v>
+        <v>-89.59999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.04799806398150585</v>
+        <v>0.1424731182795699</v>
       </c>
       <c r="AI4">
-        <v>0.04279127686795558</v>
+        <v>0.2314410480349345</v>
       </c>
       <c r="AJ4">
-        <v>8.761419053747714</v>
+        <v>-2.357894736842105</v>
       </c>
       <c r="AK4">
-        <v>1097.120884831676</v>
+        <v>4.666666666666669</v>
       </c>
       <c r="AL4">
-        <v>7.48</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>7.48</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.2099505998588567</v>
-      </c>
-      <c r="AO4">
-        <v>3.449197860962567</v>
+        <v>-0.3221884498480243</v>
       </c>
       <c r="AP4">
-        <v>-8.258527218967188</v>
-      </c>
-      <c r="AQ4">
-        <v>3.449197860962567</v>
+        <v>1.361702127659574</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +942,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aksigorta A.S. (IBSE:AKGRT)</t>
+          <t>Ray Sigorta Anonim Sirketi (IBSE:RAYSG)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,103 +951,91 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.266</v>
-      </c>
-      <c r="F5">
-        <v>0.1</v>
+        <v>0.348</v>
+      </c>
+      <c r="E5">
+        <v>0.367</v>
       </c>
       <c r="G5">
-        <v>0.1786973900775923</v>
+        <v>-0.01093706293706294</v>
       </c>
       <c r="H5">
-        <v>0.1786973900775923</v>
+        <v>-0.01093706293706294</v>
       </c>
       <c r="I5">
-        <v>0.09992946155654832</v>
+        <v>-0.02895104895104895</v>
       </c>
       <c r="J5">
-        <v>0.0779884276060888</v>
+        <v>-0.0250081057787766</v>
       </c>
       <c r="K5">
-        <v>35.9</v>
+        <v>5.53</v>
       </c>
       <c r="L5">
-        <v>0.08441100399717846</v>
+        <v>0.07734265734265734</v>
       </c>
       <c r="M5">
-        <v>34.4</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.14000814000814</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.958217270194986</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>34.4</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.14000814000814</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.958217270194986</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>219.5</v>
+        <v>57.1</v>
       </c>
       <c r="V5">
-        <v>0.8933658933658934</v>
+        <v>0.306989247311828</v>
       </c>
       <c r="W5">
-        <v>0.2785104732350659</v>
+        <v>0.1259681093394077</v>
       </c>
       <c r="X5">
-        <v>0.09335742948749436</v>
+        <v>0.1576834942450639</v>
       </c>
       <c r="Y5">
-        <v>0.1851530437475715</v>
-      </c>
-      <c r="Z5">
-        <v>-10.14067715784454</v>
-      </c>
-      <c r="AA5">
-        <v>-0.7908554664012774</v>
+        <v>-0.03171538490565615</v>
       </c>
       <c r="AB5">
-        <v>0.09278025572916694</v>
-      </c>
-      <c r="AC5">
-        <v>-0.8836357221304443</v>
+        <v>0.1575659542066057</v>
       </c>
       <c r="AD5">
-        <v>3.87</v>
+        <v>0.405</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3.87</v>
+        <v>0.405</v>
       </c>
       <c r="AG5">
-        <v>-215.63</v>
+        <v>-56.695</v>
       </c>
       <c r="AH5">
-        <v>0.01550667147493689</v>
+        <v>0.002172688500844934</v>
       </c>
       <c r="AI5">
-        <v>0.03225806451612903</v>
+        <v>0.01242140775954608</v>
       </c>
       <c r="AJ5">
-        <v>-7.17093448619887</v>
+        <v>-0.4384594563241947</v>
       </c>
       <c r="AK5">
-        <v>2.166482467597709</v>
+        <v>2.314553990610329</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1092,10 +1044,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>0.08251599147121536</v>
+        <v>-0.313953488372093</v>
       </c>
       <c r="AP5">
-        <v>-4.597654584221749</v>
+        <v>43.94961240310077</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/turkey/turkey_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_insurance_prop_cas.xlsx
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.279</v>
+        <v>0.494</v>
       </c>
       <c r="E2">
-        <v>0.388</v>
+        <v>0.8029999999999999</v>
       </c>
       <c r="F2">
-        <v>0.05</v>
+        <v>0.86</v>
       </c>
       <c r="G2">
-        <v>-0.1290203918432627</v>
+        <v>-0.04637969804047543</v>
       </c>
       <c r="H2">
-        <v>-0.1290203918432627</v>
+        <v>-0.04637969804047543</v>
       </c>
       <c r="I2">
-        <v>-0.2409671815703175</v>
+        <v>0.1226662383552843</v>
       </c>
       <c r="J2">
-        <v>-0.2182798571441057</v>
+        <v>0.1125376688865684</v>
       </c>
       <c r="K2">
-        <v>24.13</v>
+        <v>304.4</v>
       </c>
       <c r="L2">
-        <v>0.02412035185925629</v>
+        <v>0.1955669771924189</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -636,64 +636,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>346.1</v>
+        <v>526.3000000000001</v>
       </c>
       <c r="V2">
-        <v>0.4655010087424344</v>
+        <v>0.201485394892998</v>
       </c>
       <c r="W2">
-        <v>0.1259681093394077</v>
+        <v>0.9875776397515528</v>
       </c>
       <c r="X2">
-        <v>0.1589646499030975</v>
+        <v>0.1325567183530428</v>
       </c>
       <c r="Y2">
-        <v>-0.03299654056368978</v>
+        <v>0.8550209213985099</v>
+      </c>
+      <c r="Z2">
+        <v>278.2942964419811</v>
       </c>
       <c r="AB2">
-        <v>0.1579874891624672</v>
+        <v>0.1322149877328709</v>
       </c>
       <c r="AD2">
-        <v>26.075</v>
+        <v>35.127</v>
       </c>
       <c r="AE2">
-        <v>2.492842214728361</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>28.56784221472836</v>
+        <v>35.127</v>
       </c>
       <c r="AG2">
-        <v>-317.5321577852716</v>
+        <v>-491.1730000000001</v>
       </c>
       <c r="AH2">
-        <v>0.03700172530535605</v>
+        <v>0.01326935695352155</v>
       </c>
       <c r="AI2">
-        <v>0.09174949478253164</v>
+        <v>0.05656275814095039</v>
       </c>
       <c r="AJ2">
-        <v>-0.7454369234408195</v>
+        <v>-0.2315841139275421</v>
       </c>
       <c r="AK2">
-        <v>9.142310125054294</v>
+        <v>-5.185142567588971</v>
       </c>
       <c r="AL2">
-        <v>5.72</v>
+        <v>11.2</v>
       </c>
       <c r="AM2">
-        <v>5.72</v>
+        <v>11.2</v>
       </c>
       <c r="AN2">
-        <v>-0.1123026896655684</v>
+        <v>0.1772300706357215</v>
       </c>
       <c r="AO2">
-        <v>-42.11013986013986</v>
+        <v>17.04732142857143</v>
       </c>
       <c r="AP2">
-        <v>1.367582564701732</v>
+        <v>-2.478168516649849</v>
       </c>
       <c r="AQ2">
-        <v>-42.11013986013986</v>
+        <v>17.04732142857143</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anadolu Anonim Türk Sigorta Sirketi (IBSE:ANSGR)</t>
+          <t>Ray Sigorta Anonim Sirketi (IBSE:RAYSG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,31 +716,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.266</v>
+        <v>0.626</v>
       </c>
       <c r="E3">
-        <v>0.409</v>
-      </c>
-      <c r="F3">
-        <v>0.05</v>
+        <v>0.8029999999999999</v>
       </c>
       <c r="G3">
-        <v>-0.1946138967415563</v>
+        <v>0.05593575418994413</v>
       </c>
       <c r="H3">
-        <v>-0.1946138967415563</v>
+        <v>0.05593575418994413</v>
       </c>
       <c r="I3">
-        <v>-0.2541192805281143</v>
+        <v>0.1738826815642458</v>
       </c>
       <c r="J3">
-        <v>-0.2169518345768567</v>
+        <v>0.159350699531499</v>
       </c>
       <c r="K3">
-        <v>43.4</v>
+        <v>31.8</v>
       </c>
       <c r="L3">
-        <v>0.06457372414819224</v>
+        <v>0.2220670391061453</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,64 +761,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>178.2</v>
+        <v>114.7</v>
       </c>
       <c r="V3">
-        <v>0.4145150034891835</v>
+        <v>0.08757730778040773</v>
       </c>
       <c r="W3">
-        <v>0.1546685673556664</v>
+        <v>0.9875776397515528</v>
       </c>
       <c r="X3">
-        <v>0.1589646499030975</v>
+        <v>0.1319556315274657</v>
       </c>
       <c r="Y3">
-        <v>-0.004296082547431107</v>
+        <v>0.8556220082240871</v>
       </c>
       <c r="AB3">
-        <v>0.1579874891624672</v>
+        <v>0.1319492194995069</v>
       </c>
       <c r="AD3">
-        <v>4.47</v>
+        <v>0.217</v>
       </c>
       <c r="AE3">
-        <v>2.492842214728361</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.962842214728361</v>
+        <v>0.217</v>
       </c>
       <c r="AG3">
-        <v>-171.2371577852716</v>
+        <v>-114.483</v>
       </c>
       <c r="AH3">
-        <v>0.01593827980294547</v>
+        <v>0.0001656593509359753</v>
       </c>
       <c r="AI3">
-        <v>0.03720205427709857</v>
+        <v>0.003277104066931453</v>
       </c>
       <c r="AJ3">
-        <v>-0.6620091093065447</v>
+        <v>-0.09578428017673778</v>
       </c>
       <c r="AK3">
-        <v>-19.10522953353823</v>
+        <v>2.361301899634924</v>
       </c>
       <c r="AL3">
-        <v>5.72</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>5.72</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>-0.02707532027014749</v>
-      </c>
-      <c r="AO3">
-        <v>-29.82517482517483</v>
+        <v>0.0084765625</v>
       </c>
       <c r="AP3">
-        <v>1.037203778341389</v>
-      </c>
-      <c r="AQ3">
-        <v>-29.82517482517483</v>
+        <v>-4.4719921875</v>
       </c>
     </row>
     <row r="4">
@@ -838,25 +832,31 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.279</v>
+        <v>0.369</v>
+      </c>
+      <c r="E4">
+        <v>0.366</v>
+      </c>
+      <c r="F4">
+        <v>0.86</v>
       </c>
       <c r="G4">
-        <v>0.009774143302180684</v>
+        <v>-0.1111431039447164</v>
       </c>
       <c r="H4">
-        <v>0.009774143302180684</v>
+        <v>-0.1111431039447164</v>
       </c>
       <c r="I4">
-        <v>-0.2655763239875389</v>
+        <v>0.02052980132450331</v>
       </c>
       <c r="J4">
-        <v>-0.2655763239875389</v>
+        <v>0.02052980132450331</v>
       </c>
       <c r="K4">
-        <v>-24.8</v>
+        <v>35.8</v>
       </c>
       <c r="L4">
-        <v>-0.09657320872274143</v>
+        <v>0.1030809098761877</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -865,7 +865,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -874,52 +874,52 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>110.8</v>
+        <v>138.8</v>
       </c>
       <c r="V4">
-        <v>0.8683385579937304</v>
+        <v>0.4849755415793152</v>
       </c>
       <c r="W4">
-        <v>-0.2136089577950043</v>
+        <v>0.5085227272727272</v>
       </c>
       <c r="X4">
-        <v>0.1726679379346905</v>
+        <v>0.1325567183530428</v>
       </c>
       <c r="Y4">
-        <v>-0.3862768957296948</v>
+        <v>0.3759660089196843</v>
       </c>
       <c r="AB4">
-        <v>0.1628254198154563</v>
+        <v>0.1322149877328709</v>
       </c>
       <c r="AD4">
-        <v>21.2</v>
+        <v>2.51</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>21.2</v>
+        <v>2.51</v>
       </c>
       <c r="AG4">
-        <v>-89.59999999999999</v>
+        <v>-136.29</v>
       </c>
       <c r="AH4">
-        <v>0.1424731182795699</v>
+        <v>0.008693845034810016</v>
       </c>
       <c r="AI4">
-        <v>0.2314410480349345</v>
+        <v>0.02502243046555677</v>
       </c>
       <c r="AJ4">
-        <v>-2.357894736842105</v>
+        <v>-0.9091454872923758</v>
       </c>
       <c r="AK4">
-        <v>4.666666666666669</v>
+        <v>3.540919719407637</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -928,10 +928,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-0.3221884498480243</v>
+        <v>0.246078431372549</v>
       </c>
       <c r="AP4">
-        <v>1.361702127659574</v>
+        <v>-13.36176470588236</v>
       </c>
     </row>
     <row r="5">
@@ -942,7 +942,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ray Sigorta Anonim Sirketi (IBSE:RAYSG)</t>
+          <t>Anadolu Anonim Türk Sigorta Sirketi (IBSE:ANSGR)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -951,28 +951,28 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.348</v>
+        <v>0.494</v>
       </c>
       <c r="E5">
-        <v>0.367</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G5">
-        <v>-0.01093706293706294</v>
+        <v>-0.03902439024390244</v>
       </c>
       <c r="H5">
-        <v>-0.01093706293706294</v>
+        <v>-0.03902439024390244</v>
       </c>
       <c r="I5">
-        <v>-0.02895104895104895</v>
+        <v>0.14906191369606</v>
       </c>
       <c r="J5">
-        <v>-0.0250081057787766</v>
+        <v>0.1245953447342994</v>
       </c>
       <c r="K5">
-        <v>5.53</v>
+        <v>236.8</v>
       </c>
       <c r="L5">
-        <v>0.07734265734265734</v>
+        <v>0.2221388367729831</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -996,58 +996,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>57.1</v>
+        <v>272.8</v>
       </c>
       <c r="V5">
-        <v>0.306989247311828</v>
+        <v>0.2684510923046645</v>
       </c>
       <c r="W5">
-        <v>0.1259681093394077</v>
+        <v>1.314095449500555</v>
       </c>
       <c r="X5">
-        <v>0.1576834942450639</v>
+        <v>0.134171375004313</v>
       </c>
       <c r="Y5">
-        <v>-0.03171538490565615</v>
+        <v>1.179924074496242</v>
+      </c>
+      <c r="Z5">
+        <v>190.5953870910066</v>
+      </c>
+      <c r="AA5">
+        <v>23.74729795937121</v>
       </c>
       <c r="AB5">
-        <v>0.1575659542066057</v>
+        <v>0.1328451070877499</v>
+      </c>
+      <c r="AC5">
+        <v>23.61445285228346</v>
       </c>
       <c r="AD5">
-        <v>0.405</v>
+        <v>32.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.405</v>
+        <v>32.4</v>
       </c>
       <c r="AG5">
-        <v>-56.695</v>
+        <v>-240.4</v>
       </c>
       <c r="AH5">
-        <v>0.002172688500844934</v>
+        <v>0.03089834064466908</v>
       </c>
       <c r="AI5">
-        <v>0.01242140775954608</v>
+        <v>0.07128712871287128</v>
       </c>
       <c r="AJ5">
-        <v>-0.4384594563241947</v>
+        <v>-0.3098736787831915</v>
       </c>
       <c r="AK5">
-        <v>2.314553990610329</v>
+        <v>-1.323059988992845</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="AN5">
-        <v>-0.313953488372093</v>
+        <v>0.1995073891625616</v>
+      </c>
+      <c r="AO5">
+        <v>14.1875</v>
       </c>
       <c r="AP5">
-        <v>43.94961240310077</v>
+        <v>-1.480295566502463</v>
+      </c>
+      <c r="AQ5">
+        <v>14.1875</v>
       </c>
     </row>
   </sheetData>
